--- a/artfynd/A 30876-2025 artfynd.xlsx
+++ b/artfynd/A 30876-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,6 +881,103 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126297594</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80076</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storsvedjeberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>564909</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6993022</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30876-2025 artfynd.xlsx
+++ b/artfynd/A 30876-2025 artfynd.xlsx
@@ -886,7 +886,7 @@
         <v>126297594</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30876-2025 artfynd.xlsx
+++ b/artfynd/A 30876-2025 artfynd.xlsx
@@ -886,7 +886,7 @@
         <v>126297594</v>
       </c>
       <c r="B4" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30876-2025 artfynd.xlsx
+++ b/artfynd/A 30876-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -978,6 +978,920 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126529367</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storsvedjeberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>564491</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6993118</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126529484</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91265</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storsvedjeberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>564549</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6993146</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126529370</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98395</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storsvedjeberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>564992</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6993017</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126529502</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storsvedjeberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>564549</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6993146</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126529483</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storsvedjeberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>564549</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6993146</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126529357</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storsvedjeberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>564626</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6993076</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126529362</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storsvedjeberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>564524</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6993152</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126529497</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90677</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storsvedjeberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>564549</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6993146</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126529394</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storsvedjeberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>564596</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6993106</v>
+      </c>
+      <c r="S13" t="n">
+        <v>30</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30876-2025 artfynd.xlsx
+++ b/artfynd/A 30876-2025 artfynd.xlsx
@@ -1086,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126529484</v>
+        <v>126529370</v>
       </c>
       <c r="B6" t="n">
-        <v>91265</v>
+        <v>98395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,13 +1121,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564549</v>
+        <v>564992</v>
       </c>
       <c r="R6" t="n">
-        <v>6993146</v>
+        <v>6993017</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,32 +1183,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126529370</v>
+        <v>126529484</v>
       </c>
       <c r="B7" t="n">
-        <v>98395</v>
+        <v>91265</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564992</v>
+        <v>564549</v>
       </c>
       <c r="R7" t="n">
-        <v>6993017</v>
+        <v>6993146</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126529497</v>
+        <v>126529394</v>
       </c>
       <c r="B12" t="n">
-        <v>90677</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4189</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564549</v>
+        <v>564596</v>
       </c>
       <c r="R12" t="n">
-        <v>6993146</v>
+        <v>6993106</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1766,6 +1766,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1792,32 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126529394</v>
+        <v>126529497</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>90677</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>4189</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1827,13 +1832,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564596</v>
+        <v>564549</v>
       </c>
       <c r="R13" t="n">
-        <v>6993106</v>
+        <v>6993146</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1863,11 +1868,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 30876-2025 artfynd.xlsx
+++ b/artfynd/A 30876-2025 artfynd.xlsx
@@ -1086,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126529370</v>
+        <v>126529484</v>
       </c>
       <c r="B6" t="n">
-        <v>98395</v>
+        <v>91265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,13 +1121,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564992</v>
+        <v>564549</v>
       </c>
       <c r="R6" t="n">
-        <v>6993017</v>
+        <v>6993146</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,32 +1183,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126529484</v>
+        <v>126529370</v>
       </c>
       <c r="B7" t="n">
-        <v>91265</v>
+        <v>98395</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564549</v>
+        <v>564992</v>
       </c>
       <c r="R7" t="n">
-        <v>6993146</v>
+        <v>6993017</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126529394</v>
+        <v>126529497</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>90677</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>4189</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564596</v>
+        <v>564549</v>
       </c>
       <c r="R12" t="n">
-        <v>6993106</v>
+        <v>6993146</v>
       </c>
       <c r="S12" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1766,11 +1766,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,32 +1792,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126529497</v>
+        <v>126529394</v>
       </c>
       <c r="B13" t="n">
-        <v>90677</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4189</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,13 +1827,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564549</v>
+        <v>564596</v>
       </c>
       <c r="R13" t="n">
-        <v>6993146</v>
+        <v>6993106</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1868,6 +1863,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 30876-2025 artfynd.xlsx
+++ b/artfynd/A 30876-2025 artfynd.xlsx
@@ -1086,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126529370</v>
+        <v>126529484</v>
       </c>
       <c r="B6" t="n">
-        <v>98395</v>
+        <v>91339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,13 +1121,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564992</v>
+        <v>564549</v>
       </c>
       <c r="R6" t="n">
-        <v>6993017</v>
+        <v>6993146</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,32 +1183,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126529484</v>
+        <v>126529370</v>
       </c>
       <c r="B7" t="n">
-        <v>91265</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564549</v>
+        <v>564992</v>
       </c>
       <c r="R7" t="n">
-        <v>6993146</v>
+        <v>6993017</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,44 +1280,43 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126529483</v>
+        <v>126529502</v>
       </c>
       <c r="B8" t="n">
-        <v>56849</v>
+        <v>57654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
@@ -1386,43 +1385,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126529502</v>
+        <v>126529483</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>56849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
@@ -1494,7 +1494,7 @@
         <v>126529357</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>126529362</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>126529497</v>
       </c>
       <c r="B12" t="n">
-        <v>90677</v>
+        <v>90751</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30876-2025 artfynd.xlsx
+++ b/artfynd/A 30876-2025 artfynd.xlsx
@@ -983,7 +983,7 @@
         <v>126529367</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>126529394</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30876-2025 artfynd.xlsx
+++ b/artfynd/A 30876-2025 artfynd.xlsx
@@ -983,7 +983,7 @@
         <v>126529367</v>
       </c>
       <c r="B5" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>126529394</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30876-2025 artfynd.xlsx
+++ b/artfynd/A 30876-2025 artfynd.xlsx
@@ -983,7 +983,7 @@
         <v>126529367</v>
       </c>
       <c r="B5" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>126529394</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30876-2025 artfynd.xlsx
+++ b/artfynd/A 30876-2025 artfynd.xlsx
@@ -983,7 +983,7 @@
         <v>126529367</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>126529394</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30876-2025 artfynd.xlsx
+++ b/artfynd/A 30876-2025 artfynd.xlsx
@@ -983,7 +983,7 @@
         <v>126529367</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>57861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30876-2025 artfynd.xlsx
+++ b/artfynd/A 30876-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124175010</v>
+        <v>126529497</v>
       </c>
       <c r="B2" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>4189</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564846</v>
+        <v>564549</v>
       </c>
       <c r="R2" t="n">
-        <v>6992989</v>
+        <v>6993146</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -749,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125173199</v>
+        <v>126529484</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564432</v>
+        <v>564549</v>
       </c>
       <c r="R3" t="n">
-        <v>6993120</v>
+        <v>6993146</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -851,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +872,7 @@
         <v>126297594</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,14 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126529367</v>
+        <v>125173199</v>
       </c>
       <c r="B5" t="n">
-        <v>57881</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1008,14 +994,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1024,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564491</v>
+        <v>564432</v>
       </c>
       <c r="R5" t="n">
-        <v>6993118</v>
+        <v>6993120</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1054,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,45 +1068,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126529484</v>
+        <v>126529367</v>
       </c>
       <c r="B6" t="n">
-        <v>91339</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564549</v>
+        <v>564491</v>
       </c>
       <c r="R6" t="n">
-        <v>6993146</v>
+        <v>6993118</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1183,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126529370</v>
+        <v>126529502</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,37 +1185,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564992</v>
+        <v>564549</v>
       </c>
       <c r="R7" t="n">
-        <v>6993017</v>
+        <v>6993146</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,10 +1279,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126529502</v>
+        <v>126529394</v>
       </c>
       <c r="B8" t="n">
-        <v>57654</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,16 +1290,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1309,27 +1308,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564549</v>
+        <v>564596</v>
       </c>
       <c r="R8" t="n">
-        <v>6993146</v>
+        <v>6993106</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,6 +1350,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,7 +1384,7 @@
         <v>126529483</v>
       </c>
       <c r="B9" t="n">
-        <v>56849</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,48 +1487,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126529357</v>
+        <v>124175010</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>57132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564626</v>
+        <v>564846</v>
       </c>
       <c r="R10" t="n">
-        <v>6993076</v>
+        <v>6992989</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1556,22 +1556,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>08:18</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>08:18</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,32 +1588,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126529362</v>
+        <v>126529370</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>99153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564524</v>
+        <v>564992</v>
       </c>
       <c r="R11" t="n">
-        <v>6993152</v>
+        <v>6993017</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1695,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126529497</v>
+        <v>125201820</v>
       </c>
       <c r="B12" t="n">
-        <v>90751</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4189</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,13 +1720,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564549</v>
+        <v>564927</v>
       </c>
       <c r="R12" t="n">
-        <v>6993146</v>
+        <v>6993055</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1760,12 +1750,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1792,32 +1782,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126529394</v>
+        <v>126529357</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1827,13 +1817,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564596</v>
+        <v>564626</v>
       </c>
       <c r="R13" t="n">
-        <v>6993106</v>
+        <v>6993076</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1860,14 +1850,19 @@
           <t>2025-07-08</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-08</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,6 +1886,103 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126529362</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storsvedjeberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>564524</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6993152</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30876-2025 artfynd.xlsx
+++ b/artfynd/A 30876-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126297594</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175010</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126529370</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125201820</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126529497</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126529484</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125173199</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126529367</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1571,6 +1616,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126529502</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1673,6 +1723,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126529394</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126529483</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126529357</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1983,8 +2048,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126529362</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>